--- a/artfynd/S 925-2026 artfynd.xlsx
+++ b/artfynd/S 925-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74573203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74624493</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/835581</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74983083</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537626</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103030007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1492,6 +1527,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72159820</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103029996</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1744,6 +1789,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103029997</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1855,6 +1905,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74770469</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1966,6 +2021,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73983190</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2077,6 +2137,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74965504</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2187,6 +2252,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103055143</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103055148</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2407,6 +2482,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103055153</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2517,6 +2597,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103055182</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2627,6 +2712,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103137694</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2737,6 +2827,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103137699</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2847,6 +2942,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103137704</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2957,6 +3057,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103137707</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3072,6 +3177,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103174718</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3183,6 +3293,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74561127</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3294,6 +3409,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552785</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3405,6 +3525,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74723918</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3515,6 +3640,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042570</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3625,6 +3755,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042577</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3735,6 +3870,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042579</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3845,6 +3985,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042586</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3955,8 +4100,44 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103042590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>